--- a/02_Tier/02_WorkProduct/doc/engineering/SoftwareComponentVerificationAndIntegrationVerification/ENG-SWE5-003_SW 통합시험 결과서.xlsx
+++ b/02_Tier/02_WorkProduct/doc/engineering/SoftwareComponentVerificationAndIntegrationVerification/ENG-SWE5-003_SW 통합시험 결과서.xlsx
@@ -626,8 +626,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -918,6 +918,191 @@
         </is>
       </c>
       <c r="G13" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>IT-P2-01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SWR-007</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>RELEASE (기대와 일치)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>tests/integration/test_phase2_safety_priority_integration.py::test_crashAloneReleasesRegardlessOfApproachRisk</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>IT-P2-02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SWR-005</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LOCK (기대와 일치)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>tests/integration/test_phase2_safety_priority_integration.py::test_approachRiskAloneLocksWhenNoCrash</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>IT-P2-03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SWR-007, SWR-005</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>RELEASE, 우선순위 규칙 확인됨</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>tests/integration/test_phase2_safety_priority_integration.py::test_crashConfirmedOverridesApproachRiskLock</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>IT-P2-04</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SWR-021, SWR-007, SWR-005</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>HOLD_LAST_OUTPUT (기대와 일치)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>tests/integration/test_phase2_safety_priority_integration.py::test_sensorFaultGateOverridesBothPolicies</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>IT-P2-05</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SWR-013, SWR-007</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>DEGRADED=True, RELEASE 둘 다 확인</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>tests/integration/test_phase2_safety_priority_integration.py::test_staleInputStillAllowsIndependentDegradedCheck</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
@@ -950,8 +1135,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -1157,6 +1342,47 @@
       <c r="I10" s="42" t="inlineStr">
         <is>
           <t>함수커버리지 100%, 콜커버리지 100%, branch coverage 100%. HIL/실차 범위 밖.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RUN-P2-01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BL-INT-0.2 (Phase2)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PC/SIL (.venv, Python 3.14.7)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>함수커버리지 100%, 콜커버리지 100%, branch coverage 100%. PriorityArbiter 본체는 Phase 5에서 검증.</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1414,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>

--- a/02_Tier/02_WorkProduct/doc/engineering/SoftwareComponentVerificationAndIntegrationVerification/ENG-SWE5-003_SW 통합시험 결과서.xlsx
+++ b/02_Tier/02_WorkProduct/doc/engineering/SoftwareComponentVerificationAndIntegrationVerification/ENG-SWE5-003_SW 통합시험 결과서.xlsx
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1103,6 +1103,228 @@
         </is>
       </c>
       <c r="G18" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>IT-P3-01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SWR-017</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>RELEASE (기대와 일치)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>tests/integration/test_phase3_forced_priority_integration.py::test_forcedReleaseAloneReleases</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>IT-P3-02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SWR-017, SWR-005</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>RELEASE, 우선순위 확인됨</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>tests/integration/test_phase3_forced_priority_integration.py::test_forcedReleaseOverridesApproachRiskLock</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>IT-P3-03</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SWR-018, SWR-020</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LOCK, 우선순위 확인됨</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>tests/integration/test_phase3_forced_priority_integration.py::test_isofixOverridesIgnitionOff</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>IT-P3-04</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SWR-007, SWR-017</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>RELEASE (기대와 일치)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>tests/integration/test_phase3_forced_priority_integration.py::test_crashOverridesForcedReleaseTiedResult</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>IT-P3-05</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SWR-021, SWR-017, SWR-018</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HOLD_LAST_OUTPUT (기대와 일치)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>tests/integration/test_phase3_forced_priority_integration.py::test_sensorFaultGateOverridesForcedReleaseAndIsofix</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>IT-P3-06</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>vote 없음 (기대와 일치)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>tests/integration/test_phase3_forced_priority_integration.py::test_noHazardsProduceNoVoteAcrossAllPhase3Policies</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
@@ -1135,7 +1357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1383,6 +1605,47 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>함수커버리지 100%, 콜커버리지 100%, branch coverage 100%. PriorityArbiter 본체는 Phase 5에서 검증.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RUN-P3-01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BL-INT-0.3 (Phase3)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PC/SIL (.venv, Python 3.14.7)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>함수커버리지 100%, 콜커버리지 100%, branch coverage 100%.</t>
         </is>
       </c>
     </row>
